--- a/avionica/seleccion_sensores.xlsx
+++ b/avionica/seleccion_sensores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edenrochman/Library/Mobile Documents/com~apple~CloudDocs/Universidad de Valencia/faraday/avionica/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_3FB059801122E9E5821083B72F0372D4B7AB52C7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_51E158951122E9E5821083B72FADCA551EB00CDC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15160" yWindow="840" windowWidth="15000" windowHeight="18700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,9 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="144">
-  <si>
-    <t>Ejercicio 2a · Faraday Rocketry UPV</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="145">
+  <si>
+    <t>Selección de sensores: aviónica de vuelo</t>
+  </si>
+  <si>
+    <t>Faraday Rocketry UPV, ejercicio 2a</t>
   </si>
   <si>
     <t>IMU (acelerómetro + giroscopio)</t>
@@ -106,7 +109,7 @@
     <t>Frecuencia máxima (ODR)</t>
   </si>
   <si>
-    <t>Acel. 1600 Hz · Giro 2000 Hz</t>
+    <t>Acel. 1600 Hz, giro 2000 Hz</t>
   </si>
   <si>
     <t>32 kHz</t>
@@ -207,10 +210,10 @@
     <t>Resolución</t>
   </si>
   <si>
-    <t>8 bits · 780 mg/dígito (±100 g)</t>
-  </si>
-  <si>
-    <t>13 bits · 49 mg/LSB</t>
+    <t>8 bits, 780 mg/dígito (±100 g)</t>
+  </si>
+  <si>
+    <t>13 bits, 49 mg/LSB</t>
   </si>
   <si>
     <t>1000 Hz</t>
@@ -365,7 +368,7 @@
     <t>Límites de funcionamiento</t>
   </si>
   <si>
-    <t>≤ 4 g · 80 km · 500 m/s</t>
+    <t>≤ 4 g, 80 km, 500 m/s</t>
   </si>
   <si>
     <t>UART / I²C</t>
@@ -472,13 +475,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
@@ -526,15 +522,24 @@
       <sz val="12"/>
       <color rgb="FF1F3A5F"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -549,6 +554,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3A5F"/>
       </patternFill>
     </fill>
   </fills>
@@ -608,54 +618,54 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4"/>
   </cellStyleXfs>
   <cellXfs count="19">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -971,14 +981,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17"/>
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -986,7 +998,7 @@
     </row>
     <row r="4" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -994,205 +1006,205 @@
     </row>
     <row r="5" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="12"/>
     </row>
     <row r="19" spans="1:4" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="12"/>
     </row>
     <row r="21" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -1200,145 +1212,145 @@
     </row>
     <row r="22" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="12"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D23" s="3"/>
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D24" s="5"/>
     </row>
     <row r="25" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D25" s="5"/>
     </row>
     <row r="26" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D27" s="5"/>
     </row>
     <row r="28" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D28" s="5"/>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D29" s="5"/>
     </row>
     <row r="30" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D30" s="5"/>
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="12"/>
     </row>
     <row r="33" spans="1:4" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="12"/>
     </row>
     <row r="35" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -1346,169 +1358,169 @@
     </row>
     <row r="36" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="12"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D37" s="3"/>
     </row>
     <row r="38" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" s="5"/>
     </row>
     <row r="39" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D39" s="5"/>
     </row>
     <row r="40" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D40" s="5"/>
     </row>
     <row r="41" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D41" s="5"/>
     </row>
     <row r="42" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D42" s="5"/>
     </row>
     <row r="43" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D43" s="5"/>
     </row>
     <row r="44" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D44" s="5"/>
     </row>
     <row r="45" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D45" s="5"/>
     </row>
     <row r="46" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D46" s="5"/>
     </row>
     <row r="47" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D47" s="5"/>
     </row>
     <row r="48" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="12"/>
     </row>
     <row r="49" spans="1:4" ht="130" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="12"/>
     </row>
     <row r="51" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
@@ -1516,157 +1528,157 @@
     </row>
     <row r="52" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="12"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D53" s="3"/>
     </row>
     <row r="54" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D54" s="5"/>
     </row>
     <row r="55" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D55" s="5"/>
     </row>
     <row r="56" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D56" s="5"/>
     </row>
     <row r="57" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D57" s="5"/>
     </row>
     <row r="58" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D58" s="5"/>
     </row>
     <row r="59" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D59" s="5"/>
     </row>
     <row r="60" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D60" s="5"/>
     </row>
     <row r="61" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D61" s="5"/>
     </row>
     <row r="62" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D62" s="5"/>
     </row>
     <row r="63" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="12"/>
     </row>
     <row r="64" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C64" s="11"/>
       <c r="D64" s="12"/>
     </row>
     <row r="66" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
@@ -1674,157 +1686,157 @@
     </row>
     <row r="67" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="12"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D68" s="3"/>
     </row>
     <row r="69" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D69" s="5"/>
     </row>
     <row r="70" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D70" s="5"/>
     </row>
     <row r="71" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D71" s="5"/>
     </row>
     <row r="72" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D72" s="5"/>
     </row>
     <row r="73" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D73" s="5"/>
     </row>
     <row r="74" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D74" s="5"/>
     </row>
     <row r="75" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D75" s="5"/>
     </row>
     <row r="76" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D76" s="5"/>
     </row>
     <row r="77" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D77" s="5"/>
     </row>
     <row r="78" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="12"/>
     </row>
     <row r="79" spans="1:4" ht="110" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C79" s="11"/>
       <c r="D79" s="12"/>
     </row>
     <row r="81" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
